--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -441,23 +441,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -467,32 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -504,7 +492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -512,22 +500,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>6004.0359.3714 Haufe Service Center | GmbH lx2025010084916 KHYY-YNLG | Lexware Office L | 677c926e77571fd0c58914b4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lexoffice 01 25.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -539,7 +522,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -547,27 +530,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -579,27 +552,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -607,7 +575,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -617,7 +585,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -627,7 +595,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -637,7 +605,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -655,23 +623,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -681,32 +647,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -718,27 +674,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -750,27 +701,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -782,27 +728,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -814,27 +755,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -846,7 +782,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -854,27 +790,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -886,7 +812,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -894,22 +820,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>lx2025100098014 KHYY-YNLG Lexware | Office L 68e4a6d75058ac8c6d783819 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>88aacb33-33ad-417c-8fe4-832b7e70f14f.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -921,7 +842,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -929,27 +850,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -961,27 +872,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -993,27 +899,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -1025,7 +926,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1033,22 +934,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Funnelcockpit_2.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1056,7 +952,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1066,7 +962,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1076,7 +972,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1086,7 +982,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1104,23 +1000,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1130,32 +1024,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1175,22 +1059,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>H_31943964.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1202,32 +1081,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>97</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Receipt-2172-3201.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (97.0 USD), Bankbuchung in EUR (84.32) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2172-3201.pdf)</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1111,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1247,22 +1119,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>lx2025110094793 KHYY-YNLG Lexware | Office L 690d605e5977c0f454673868 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>e2a326b2-ade7-430c-ad97-bafe06fe26ce.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1141,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>cyfire Rechtsanwaltsgesellschaft mbH</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CY-16562-MM | IBAN: DE13100180000100747895 | BIC: FNOMDEB2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Finom_payment_13112025.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - Beleg ohne Netto-/USt-Angabe</t>
         </is>
       </c>
     </row>
@@ -1311,27 +1171,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1351,22 +1206,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>hostinger.com</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>H_32869079.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1228,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1386,27 +1236,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1258,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1426,22 +1266,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250007.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1453,27 +1288,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1315,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1493,22 +1323,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>hostinger.com</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>H_33541164.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1520,27 +1345,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1368,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1558,31 +1378,31 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>76.04000000000001</v>
+        <v>623.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>348.96</v>
+        <v>-198.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1596,23 +1416,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1622,32 +1440,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1667,22 +1475,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>lx2025110349962 KHYY-YNLG Lexware | Office L 692810c71c78601ef4fb4be8 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>a9c2c58e-ea2a-45d6-a7e5-43a3744c3a21.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -1694,32 +1497,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Receipt-2265-8647.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (21.8 USD), Bankbuchung in EUR (18.76) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2265-8647.pdf)</t>
         </is>
       </c>
     </row>
@@ -1731,32 +1527,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Invoice-GMM5S7YE-0001.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'GAMMA.APP' vs. Beleg-Partner 'Invoice number GMM5S7YE-0001' (Invoice-GMM5S7YE-0001.pdf)</t>
         </is>
       </c>
     </row>
@@ -1768,27 +1557,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1584,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *UFNK69RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf)</t>
         </is>
       </c>
     </row>
@@ -1837,32 +1614,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *YHJ6S8ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf)</t>
         </is>
       </c>
     </row>
@@ -1874,32 +1644,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *XFZ769DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf)</t>
         </is>
       </c>
     </row>
@@ -1911,32 +1674,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *JFQQ29DMU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf)</t>
         </is>
       </c>
     </row>
@@ -1948,32 +1704,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *HLN339MLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf)</t>
         </is>
       </c>
     </row>
@@ -1985,32 +1734,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BMHJC8VLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf)</t>
         </is>
       </c>
     </row>
@@ -2022,32 +1764,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *WSY378HLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf)</t>
         </is>
       </c>
     </row>
@@ -2059,32 +1794,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>FACEBK *C3GR9A9MU2</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *C3GR9A9MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf)</t>
         </is>
       </c>
     </row>
@@ -2096,32 +1824,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QHNPD9DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf)</t>
         </is>
       </c>
     </row>
@@ -2133,27 +1854,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -2165,32 +1881,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>FACEBK *4Q76L9RLU2</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *4Q76L9RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf)</t>
         </is>
       </c>
     </row>
@@ -2202,32 +1911,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>FACEBK *BNNY6A5MU2</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BNNY6A5MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf)</t>
         </is>
       </c>
     </row>
@@ -2239,32 +1941,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>FACEBK *QUFFB9ZLU2</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QUFFB9ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf)</t>
         </is>
       </c>
     </row>
@@ -2276,27 +1971,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -2308,7 +1998,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2316,27 +2006,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -2348,27 +2028,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2055,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2388,22 +2063,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rechnung RE250009.pdf</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -2415,27 +2085,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 4760.0 am 2025-12-31 bei mehreren Buchungen: Benito Ferrise (EINGANG), Benito Ferrise (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -2447,27 +2112,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 4760.0 am 2025-12-31 bei mehreren Buchungen: Benito Ferrise (EINGANG), Benito Ferrise (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2139,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2487,22 +2147,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2165,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2520,31 +2175,31 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>34.52</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3965.48</v>
+        <v>3828.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2558,23 +2213,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2584,32 +2237,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2264,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2629,22 +2272,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>6032.5420.7052 Haufe Service Center | GmbH lx2025020086172 KHYY-YNLG | Lexware Office L | 67a570c6ec20eeb352fa01d4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lexoffice 02 25.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2294,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2664,27 +2302,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2320,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -2702,7 +2330,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2712,7 +2340,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2722,7 +2350,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2740,23 +2368,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2766,32 +2392,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -2803,32 +2419,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Instantly 03 25.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (37.0 USD), Bankbuchung in EUR (35.62) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 03 25.pdf)</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2848,22 +2457,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>6056.7592.6183 Haufe Service Center | GmbH lx2025030096223 KHYY-YNLG | Lexware Office L | 67ca5b67347009ebdcdfd42c | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lexoffice 03 25.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2479,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2883,27 +2487,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2505,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2921,31 +2515,31 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>44.9</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-44.9</v>
+        <v>-81.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2959,23 +2553,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2985,32 +2577,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -3022,27 +2604,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ZOHO-ZOHO CORP</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ZOHO-ZOHO CORP</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3054,27 +2631,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3086,27 +2658,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3118,7 +2685,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3126,22 +2693,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>6081.7571.6196 Haufe Service Center | GmbH lx2025040088805 KHYY-YNLG | Lexware Office L | 67f32b8cb70fd8129780e042 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lexoffice 04 25.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -3149,7 +2711,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -3159,7 +2721,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -3169,7 +2731,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -3179,7 +2741,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3197,23 +2759,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3223,32 +2783,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -3260,7 +2810,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3268,27 +2818,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -3300,27 +2840,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3332,7 +2867,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3340,22 +2875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>6109.4039.0735 Haufe Service Center | GmbH lx2025050092112 KHYY-YNLG | Lexware Office L | 681ab828156bd6b3f2273faa | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lexoffice 05 25.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -3367,27 +2897,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3399,27 +2924,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3431,7 +2951,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3439,27 +2959,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Triathlon Transfer GmbH</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>lastschriftverfahren | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -3471,27 +2981,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3503,27 +3008,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3031,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -3541,7 +3041,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -3551,7 +3051,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -3561,7 +3061,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -3579,23 +3079,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3605,32 +3103,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -3642,27 +3130,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3157,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3682,22 +3165,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>6135.3191.8492 Haufe Service Center | GmbH lx2025060090542 KHYY-YNLG | Lexware Office L | 684396535f6f8a0df6201eeb | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lexoffice 06 25.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -3709,32 +3187,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Instantly 061 25.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.41) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 061 25.pdf)</t>
         </is>
       </c>
     </row>
@@ -3746,27 +3217,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3240,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -3784,31 +3250,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>19.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-19.9</v>
+        <v>-39.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3822,23 +3288,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3848,32 +3312,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -3885,27 +3339,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3366,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3925,27 +3374,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -3957,27 +3396,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3997,22 +3431,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>6160.3778.4621 Haufe Service Center | GmbH lx2025070093981 KHYY-YNLG | Lexware Office L | 686b23a691532290558dcb3a | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lexoffice 07 25.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4024,27 +3453,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4056,27 +3480,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4084,7 +3503,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -4094,7 +3513,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -4104,7 +3523,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -4114,7 +3533,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -4132,23 +3551,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -4158,32 +3575,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -4195,27 +3602,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4227,27 +3629,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4259,27 +3656,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4291,7 +3683,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4299,27 +3691,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>APIFY* SUBSCRIPTION</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Apify_Invoice_202508060773.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (40.27) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202508060773.pdf)</t>
         </is>
       </c>
     </row>
@@ -4331,27 +3713,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4363,7 +3740,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4371,22 +3748,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lexoffice 08 25.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4398,32 +3770,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Invoice-BCE54405-0015.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.18) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0015.pdf)</t>
         </is>
       </c>
     </row>
@@ -4435,32 +3800,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Wix.com</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Wix.com</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Premium Paket 2025.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - Beleg ohne Netto-/USt-Angabe</t>
         </is>
       </c>
     </row>
@@ -4472,7 +3827,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4480,22 +3835,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rechnung Joel Wagner.pdf</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4507,27 +3857,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4539,27 +3884,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4567,7 +3907,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -4577,31 +3917,31 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>60.9</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>39.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4615,23 +3955,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="53" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zahlungsdatum</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -4641,32 +3979,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Betrag netto</t>
+          <t>Netto-Betrag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Gegenpartei</t>
+          <t>Beleg da?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Verwendungszweck</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Beleg-Datei</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Hinweis</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4686,22 +4014,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Mattha  Wimmler eGbR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Frankfurt Event | IBAN: DE63515500350002142891 | BIC: HELADEF1WET</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rechnung_RE073.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4036,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4721,27 +4044,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -4753,27 +4066,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4093,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4793,27 +4101,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>APIFY* INV#20250906015</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>APIFY* INV#20250906015</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Apify_Invoice_202509060156.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (39.91) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202509060156.pdf)</t>
         </is>
       </c>
     </row>
@@ -4825,27 +4123,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Hotel Melia Frankfurt am Main | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 82.99 am 2025-09-11 bei mehreren Buchungen: Benito Ferrise (EINGANG), Mohamed Amin Douioui (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4150,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4865,22 +4158,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>6213.9637.8151 Haufe Service Center | GmbH lx2025090092498 KHYY-YNLG | Lexware Office L | 68bce0d6a849936d9aa55352 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lexoffice 09 25.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4892,32 +4180,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Invoice-BCE54405-0017.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.07) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0017.pdf)</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4210,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4937,22 +4218,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>IONOS SE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4964,27 +4240,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>KEIN NETTO VERFUEGBAR - kein Beleg gefunden</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4267,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5004,22 +4275,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Funnelcockpit_2.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -5027,7 +4293,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SUMME Umsatz netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -5037,31 +4303,31 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SUMME Ausgaben netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>215.74</v>
+        <v>235.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GEWINN NETTO (Monat):</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-215.74</v>
+        <v>-235.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Anzahl Zahlungen OHNE Netto-Wert (nicht in Summe enthalten):</t>
+          <t>Zahlungen ohne Beleg (kein Wert):</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -1348,9 +1348,12 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>97.2</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1382,7 +1385,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>623.04</v>
+        <v>720.24</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1395,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-198.04</v>
+        <v>-295.24</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1405,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2984,9 +2987,12 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3045,7 +3051,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3055,7 +3061,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-69.90000000000001</v>
+        <v>-74.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3065,7 +3071,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3483,9 +3489,12 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3517,7 +3526,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>44.9</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="11">
@@ -3527,7 +3536,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-44.9</v>
+        <v>-49.9</v>
       </c>
     </row>
     <row r="12">
@@ -3537,7 +3546,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -28,13 +28,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,12 +47,18 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -70,12 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,15 +451,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,10 +486,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -505,10 +521,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Lexoffice 01 25.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>6004.0359.3714 Haufe Service Center | GmbH lx2025010084916 KHYY-YNLG | Lexware Office L | 677c926e77571fd0c58914b4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -535,37 +556,46 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
@@ -573,42 +603,42 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>34.95</v>
+      <c r="C7" s="3" t="n">
+        <v>39.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>-34.95</v>
+      <c r="C8" s="3" t="n">
+        <v>-39.76</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -623,15 +653,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,10 +688,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -677,17 +713,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>35.44</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0018.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -704,17 +748,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>82.83</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0019.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -731,44 +783,56 @@
           <t>Umsatz</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>231.09</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>130.34</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -795,10 +859,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -825,10 +894,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>88aacb33-33ad-417c-8fe4-832b7e70f14f.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>lx2025100098014 KHYY-YNLG Lexware | Office L 68e4a6d75058ac8c6d783819 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -855,37 +929,46 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
@@ -902,17 +985,25 @@
           <t>Umsatz</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>193.91</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
@@ -939,10 +1030,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Rechnung Clickfunnel.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -950,43 +1046,43 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
+      <c r="C13" s="3" t="n">
+        <v>555.34</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>118.9</v>
+      <c r="C14" s="3" t="n">
+        <v>244.72</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>-118.9</v>
+      <c r="C15" s="3" t="n">
+        <v>310.62</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>6</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1000,15 +1096,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,10 +1131,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1064,10 +1166,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>H_31943964.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
@@ -1094,10 +1201,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Receipt-2172-3201.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -1124,10 +1236,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>e2a326b2-ade7-430c-ad97-bafe06fe26ce.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>lx2025110094793 KHYY-YNLG Lexware | Office L 690d605e5977c0f454673868 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -1154,37 +1271,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Finom_payment_13112025.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>cyfire Rechtsanwaltsgesellschaft mbH</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>CY-16562-MM | IBAN: DE13100180000100747895 | BIC: FNOMDEB2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
@@ -1211,10 +1337,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>H_32869079.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
@@ -1241,10 +1372,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -1271,37 +1407,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Rechnung RE250007.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2025-11-23</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
@@ -1328,10 +1473,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>H_33541164.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
@@ -1358,10 +1508,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
         </is>
@@ -1369,42 +1524,42 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="3" t="n">
         <v>425</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>720.24</v>
+      <c r="C15" s="3" t="n">
+        <v>736.4299999999999</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>-295.24</v>
+      <c r="C16" s="3" t="n">
+        <v>-311.43</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1419,15 +1574,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,10 +1609,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1483,10 +1644,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>a9c2c58e-ea2a-45d6-a7e5-43a3744c3a21.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>lx2025110349962 KHYY-YNLG Lexware | Office L 692810c71c78601ef4fb4be8 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -1513,10 +1679,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Receipt-2265-8647.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -1543,37 +1714,46 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Invoice-GMM5S7YE-0001.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
@@ -1600,10 +1780,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
@@ -1630,10 +1815,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
@@ -1660,10 +1850,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
@@ -1690,10 +1885,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
@@ -1720,10 +1920,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
@@ -1750,10 +1955,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
@@ -1780,10 +1990,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
@@ -1810,10 +2025,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>FACEBK *C3GR9A9MU2</t>
         </is>
@@ -1840,37 +2060,46 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -1897,10 +2126,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>FACEBK *4Q76L9RLU2</t>
         </is>
@@ -1927,10 +2161,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>FACEBK *BNNY6A5MU2</t>
         </is>
@@ -1957,37 +2196,46 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2025-12-23</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
@@ -2014,37 +2262,46 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2025-12-25</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
@@ -2071,64 +2328,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Rechnung RE250009.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2155,10 +2425,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -2166,42 +2441,42 @@
     </row>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>4000</v>
+      <c r="C27" s="3" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>171.32</v>
+      <c r="C28" s="3" t="n">
+        <v>4219.19</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>3828.68</v>
+      <c r="C29" s="3" t="n">
+        <v>3780.81</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2216,15 +2491,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2250,10 +2526,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -2280,10 +2561,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Lexoffice 02 25.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>6032.5420.7052 Haufe Service Center | GmbH lx2025020086172 KHYY-YNLG | Lexware Office L | 67a570c6ec20eeb352fa01d4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2310,10 +2596,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2321,42 +2612,42 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>44.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>-44.9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2371,15 +2662,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2405,10 +2697,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -2435,10 +2732,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Instantly 03 25.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2465,10 +2767,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Lexoffice 03 25.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>6056.7592.6183 Haufe Service Center | GmbH lx2025030096223 KHYY-YNLG | Lexware Office L | 67ca5b67347009ebdcdfd42c | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2495,10 +2802,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2506,42 +2818,42 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>81.90000000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>-81.90000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2556,15 +2868,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2590,37 +2903,46 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ZOHO-ZOHO CORP</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ZOHO-ZOHO CORP</t>
         </is>
@@ -2637,17 +2959,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>34.13</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Instantly 04 25.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2664,17 +2994,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>33.32</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Instantly 041 25.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2701,10 +3039,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Lexoffice 04 25.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>6081.7571.6196 Haufe Service Center | GmbH lx2025040088805 KHYY-YNLG | Lexware Office L | 67f32b8cb70fd8129780e042 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2712,43 +3055,43 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>19.9</v>
+      <c r="C8" s="3" t="n">
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>-19.9</v>
+      <c r="C9" s="3" t="n">
+        <v>-98.15000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>3</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2762,15 +3105,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2796,10 +3140,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -2826,10 +3175,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2846,17 +3200,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>32.82</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Instantly 050 25.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2883,10 +3245,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Lexoffice 05 25.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>6109.4039.0735 Haufe Service Center | GmbH lx2025050092112 KHYY-YNLG | Lexware Office L | 681ab828156bd6b3f2273faa | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2903,17 +3270,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>17.91</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Instantly 051 25.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2930,17 +3305,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>29.54</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Instantly 05 25.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2967,10 +3350,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Triathlon Transfer GmbH</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>lastschriftverfahren | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2997,10 +3385,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
         </is>
@@ -3017,17 +3410,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>17.73</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -3035,43 +3436,43 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>74.90000000000001</v>
+      <c r="C12" s="3" t="n">
+        <v>172.9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>-74.90000000000001</v>
+      <c r="C13" s="3" t="n">
+        <v>-172.9</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>4</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3085,15 +3486,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3119,10 +3521,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3139,17 +3546,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>85.37</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Instantly 06 25.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3176,10 +3591,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Lexoffice 06 25.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>6135.3191.8492 Haufe Service Center | GmbH lx2025060090542 KHYY-YNLG | Lexware Office L | 684396535f6f8a0df6201eeb | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3206,10 +3626,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Instantly 061 25.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3226,17 +3651,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>17.12</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Invoice-LRDKYW8R-0002.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -3244,43 +3677,43 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>39.9</v>
+      <c r="C8" s="3" t="n">
+        <v>142.39</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>-39.9</v>
+      <c r="C9" s="3" t="n">
+        <v>-142.39</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3294,15 +3727,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3328,10 +3762,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3348,17 +3787,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>82.79000000000001</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0010.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3385,10 +3832,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -3405,17 +3857,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Paddle n8n Cloud Beleg 10-07-2025.md</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
@@ -3442,37 +3902,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Lexoffice 07 25.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>6160.3778.4621 Haufe Service Center | GmbH lx2025070093981 KHYY-YNLG | Lexware Office L | 686b23a691532290558dcb3a | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -3499,10 +3968,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
         </is>
@@ -3510,43 +3984,43 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
+      <c r="C9" s="3" t="n">
+        <v>21.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>49.9</v>
+      <c r="C10" s="3" t="n">
+        <v>156.69</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>-49.9</v>
+      <c r="C11" s="3" t="n">
+        <v>-135.19</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>3</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3560,15 +4034,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3594,10 +4069,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3614,71 +4094,87 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>52.17</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0014.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -3705,37 +4201,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Apify_Invoice_202508060773.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -3762,10 +4267,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Lexoffice 08 25.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3792,10 +4302,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0015.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3819,10 +4334,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Premium Paket 2025.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Wix.com</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Wix.com</t>
         </is>
@@ -3849,37 +4369,46 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Rechnung Joel Wagner.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
@@ -3896,17 +4425,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>47</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Funnelcockpit_2.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -3914,43 +4451,43 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>100</v>
+      <c r="C14" s="3" t="n">
+        <v>178.38</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>80.90000000000001</v>
+      <c r="C15" s="3" t="n">
+        <v>188.99</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>19.1</v>
+      <c r="C16" s="3" t="n">
+        <v>-10.61</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>6</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3964,15 +4501,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3998,10 +4536,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Beleg-Dateiname</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -4028,10 +4571,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Rechnung_RE073.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Mattha  Wimmler eGbR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt Event | IBAN: DE63515500350002142891 | BIC: HELADEF1WET</t>
         </is>
@@ -4058,10 +4606,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -4078,17 +4631,25 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>83.58</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0016.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -4115,37 +4676,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Apify_Invoice_202509060156.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>APIFY* INV#20250906015</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>APIFY* INV#20250906015</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Hotel Melia Frankfurt am Main | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -4172,10 +4742,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Lexoffice 09 25.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>6213.9637.8151 Haufe Service Center | GmbH lx2025090092498 KHYY-YNLG | Lexware Office L | 68bce0d6a849936d9aa55352 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -4202,10 +4777,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Invoice-BCE54405-0017.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -4232,67 +4812,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -4300,42 +4890,42 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Umsatz netto:</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Ausgabe netto:</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>235.74</v>
+      <c r="C14" s="3" t="n">
+        <v>396.61</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>GEWINN/VERLUST:</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>-235.74</v>
+      <c r="C15" s="3" t="n">
+        <v>-396.61</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Zahlungen ohne Beleg (kein Wert):</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +37,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -46,8 +47,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,14 +60,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,13 +89,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,16 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,20 +493,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -521,15 +538,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lexoffice 01 25.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>6004.0359.3714 Haufe Service Center | GmbH lx2025010084916 KHYY-YNLG | Lexware Office L | 677c926e77571fd0c58914b4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -556,15 +578,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -586,16 +613,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
@@ -619,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>39.76</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +661,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-39.76</v>
+        <v>-34.95</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +685,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,20 +716,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -718,20 +756,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0018.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -753,20 +796,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0019.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -793,15 +841,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Rechnung Vapi Martin Veser.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
@@ -823,16 +876,21 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Nein - Finanzamt (steuerneutral)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -859,15 +917,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -894,15 +957,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>88aacb33-33ad-417c-8fe4-832b7e70f14f.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>lx2025100098014 KHYY-YNLG Lexware | Office L 68e4a6d75058ac8c6d783819 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -929,15 +997,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -959,16 +1032,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
@@ -995,15 +1073,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Rechnung Vapi Martin Veser.pdf</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
@@ -1030,15 +1113,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Rechnung Clickfunnel.pdf</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -1052,7 +1140,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>555.34</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -1062,7 +1150,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>244.72</v>
+        <v>237.17</v>
       </c>
     </row>
     <row r="15">
@@ -1072,7 +1160,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>310.62</v>
+        <v>187.83</v>
       </c>
     </row>
     <row r="16">
@@ -1096,16 +1184,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,20 +1215,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1166,15 +1260,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>H_31943964.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
@@ -1196,20 +1295,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Receipt-2172-3201.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -1236,15 +1340,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>e2a326b2-ade7-430c-ad97-bafe06fe26ce.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>lx2025110094793 KHYY-YNLG Lexware | Office L 690d605e5977c0f454673868 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -1266,86 +1375,101 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Finom_payment_13112025.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>cyfire Rechtsanwaltsgesellschaft mbH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CY-16562-MM | IBAN: DE13100180000100747895 | BIC: FNOMDEB2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>1.16</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>H_32869079.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
@@ -1372,15 +1496,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -1407,15 +1536,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Rechnung RE250007.pdf</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
@@ -1437,16 +1571,21 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
@@ -1473,15 +1612,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>H_33541164.pdf</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
@@ -1508,15 +1652,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
         </is>
@@ -1540,7 +1689,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>736.4299999999999</v>
+        <v>727.72</v>
       </c>
     </row>
     <row r="16">
@@ -1550,7 +1699,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-311.43</v>
+        <v>-302.72</v>
       </c>
     </row>
     <row r="17">
@@ -1574,16 +1723,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1604,55 +1754,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>a9c2c58e-ea2a-45d6-a7e5-43a3744c3a21.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>lx2025110349962 KHYY-YNLG Lexware | Office L 692810c71c78601ef4fb4be8 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -1674,20 +1834,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Receipt-2265-8647.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -1709,20 +1874,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Invoice-GMM5S7YE-0001.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
@@ -1744,261 +1914,301 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>GAMMA.APP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
@@ -2020,86 +2230,101 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>17.92</v>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2121,20 +2346,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>FACEBK *4Q76L9RLU2</t>
         </is>
@@ -2156,20 +2386,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>FACEBK *BNNY6A5MU2</t>
         </is>
@@ -2191,20 +2426,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>FACEBK *QUFFB9ZLU2</t>
         </is>
@@ -2226,16 +2466,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
@@ -2262,46 +2507,56 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2025-12-25</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>17.99</v>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
@@ -2328,15 +2583,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Rechnung RE250009.pdf</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2358,16 +2618,21 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2389,51 +2654,61 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -2447,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="28">
@@ -2457,7 +2732,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4219.19</v>
+        <v>153.71</v>
       </c>
     </row>
     <row r="29">
@@ -2467,7 +2742,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3780.81</v>
+        <v>3846.29</v>
       </c>
     </row>
     <row r="30">
@@ -2491,16 +2766,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2521,20 +2797,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -2561,15 +2842,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lexoffice 02 25.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>6032.5420.7052 Haufe Service Center | GmbH lx2025020086172 KHYY-YNLG | Lexware Office L | 67a570c6ec20eeb352fa01d4 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2596,15 +2882,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2662,16 +2953,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2692,20 +2984,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -2727,20 +3024,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Instantly 03 25.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2767,15 +3069,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Lexoffice 03 25.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>6056.7592.6183 Haufe Service Center | GmbH lx2025030096223 KHYY-YNLG | Lexware Office L | 67ca5b67347009ebdcdfd42c | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -2802,15 +3109,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -2868,16 +3180,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2898,51 +3211,61 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>10.8</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>ZOHO-ZOHO CORP</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>ZOHO-ZOHO CORP</t>
         </is>
@@ -2964,20 +3287,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Instantly 04 25.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2999,20 +3327,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Instantly 041 25.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3039,15 +3372,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Lexoffice 04 25.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>6081.7571.6196 Haufe Service Center | GmbH lx2025040088805 KHYY-YNLG | Lexware Office L | 67f32b8cb70fd8129780e042 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3105,16 +3443,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3135,20 +3474,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3175,15 +3519,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -3205,20 +3554,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Instantly 050 25.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3245,15 +3599,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Lexoffice 05 25.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>6109.4039.0735 Haufe Service Center | GmbH lx2025050092112 KHYY-YNLG | Lexware Office L | 681ab828156bd6b3f2273faa | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3275,20 +3634,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Instantly 051 25.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3310,20 +3674,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Instantly 05 25.pdf</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3350,50 +3719,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Triathlon Transfer GmbH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>lastschriftverfahren | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
         </is>
@@ -3415,20 +3794,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -3452,7 +3836,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>172.9</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="13">
@@ -3462,7 +3846,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-172.9</v>
+        <v>-167.9</v>
       </c>
     </row>
     <row r="14">
@@ -3486,16 +3870,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3516,20 +3901,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3551,20 +3941,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Instantly 06 25.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3591,15 +3986,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Lexoffice 06 25.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>6135.3191.8492 Haufe Service Center | GmbH lx2025060090542 KHYY-YNLG | Lexware Office L | 684396535f6f8a0df6201eeb | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3621,20 +4021,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Instantly 061 25.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3656,20 +4061,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Invoice-LRDKYW8R-0002.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -3727,16 +4137,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3757,20 +4168,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -3792,20 +4208,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0010.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -3832,15 +4253,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -3867,15 +4293,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Paddle n8n Cloud Beleg 10-07-2025.md</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
@@ -3902,15 +4333,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Lexoffice 07 25.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>6160.3778.4621 Haufe Service Center | GmbH lx2025070093981 KHYY-YNLG | Lexware Office L | 686b23a691532290558dcb3a | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -3932,51 +4368,61 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Nein - Finanzamt (steuerneutral)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
         </is>
@@ -3990,7 +4436,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4000,7 +4446,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>156.69</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="11">
@@ -4010,7 +4456,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-135.19</v>
+        <v>-151.69</v>
       </c>
     </row>
     <row r="12">
@@ -4034,16 +4480,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4064,20 +4511,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -4099,20 +4551,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0014.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -4134,16 +4591,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
@@ -4165,16 +4627,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Nein - Finanzamt (steuerneutral)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -4201,15 +4668,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Apify_Invoice_202508060773.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>APIFY* SUBSCRIPTION</t>
         </is>
@@ -4231,16 +4703,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -4267,15 +4744,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Lexoffice 08 25.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -4297,20 +4779,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0015.pdf</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -4334,15 +4821,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Premium Paket 2025.pdf</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Wix.com</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Wix.com</t>
         </is>
@@ -4369,15 +4861,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Rechnung Joel Wagner.pdf</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
@@ -4399,16 +4896,21 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>OPENAI</t>
         </is>
@@ -4435,15 +4937,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Funnelcockpit_2.pdf</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -4457,7 +4964,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>178.38</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -4467,7 +4974,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>188.99</v>
+        <v>180.07</v>
       </c>
     </row>
     <row r="16">
@@ -4477,7 +4984,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-10.61</v>
+        <v>-80.06999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -4501,16 +5008,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="53" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="53" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4531,20 +5039,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -4571,15 +5084,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Rechnung_RE073.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Mattha  Wimmler eGbR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Frankfurt Event | IBAN: DE63515500350002142891 | BIC: HELADEF1WET</t>
         </is>
@@ -4606,15 +5124,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -4636,20 +5159,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0016.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -4676,46 +5204,56 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Apify_Invoice_202509060156.pdf</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>APIFY* INV#20250906015</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>APIFY* INV#20250906015</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>69.73999999999999</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Hotel Melia Frankfurt am Main | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -4742,15 +5280,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Lexoffice 09 25.pdf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>6213.9637.8151 Haufe Service Center | GmbH lx2025090092498 KHYY-YNLG | Lexware Office L | 68bce0d6a849936d9aa55352 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -4772,55 +5315,65 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Invoice-BCE54405-0017.pdf</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
@@ -4842,47 +5395,57 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>Nein - Bagatelle &lt; 10 EUR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -4906,7 +5469,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>396.61</v>
+        <v>388.22</v>
       </c>
     </row>
     <row r="15">
@@ -4916,7 +5479,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-396.61</v>
+        <v>-388.22</v>
       </c>
     </row>
     <row r="16">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -2295,36 +2295,40 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>17.92</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(kein Originalbeleg - akzeptiert)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
         </is>
@@ -2527,36 +2531,40 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2025-12-25</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>17.99</v>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>H_34974301.pdf</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>HOSTINGER* HOSTINGER.D</t>
         </is>
@@ -2752,7 +2760,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5416,36 +5424,40 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>47</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rechnung_TJC9SRX6_I-74230203-de.pdf</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
@@ -5489,7 +5501,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -468,7 +468,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -1436,40 +1436,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1.16</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>H_32869079.pdf</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>hostinger.com</t>
         </is>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>727.72</v>
+        <v>728.88</v>
       </c>
     </row>
     <row r="16">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-302.72</v>
+        <v>-303.88</v>
       </c>
     </row>
     <row r="17">
@@ -1779,40 +1779,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1.3</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>a9c2c58e-ea2a-45d6-a7e5-43a3744c3a21.pdf</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>lx2025110349962 KHYY-YNLG Lexware | Office L 692810c71c78601ef4fb4be8 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1935,280 +1935,280 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>FACEBK *WSY378HLU2</t>
         </is>
@@ -2255,40 +2255,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>FACEBK *QHNPD9DLU2</t>
         </is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2683,40 +2683,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH via Mollie</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>153.71</v>
+        <v>207.23</v>
       </c>
     </row>
     <row r="29">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3846.29</v>
+        <v>3792.77</v>
       </c>
     </row>
     <row r="30">
@@ -3457,7 +3457,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -3747,40 +3747,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
         </is>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>167.9</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="13">
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-167.9</v>
+        <v>-172.9</v>
       </c>
     </row>
     <row r="14">
@@ -4397,40 +4397,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
         </is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>151.69</v>
+        <v>156.69</v>
       </c>
     </row>
     <row r="11">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-151.69</v>
+        <v>-156.69</v>
       </c>
     </row>
     <row r="12">
@@ -4494,7 +4494,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="53" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -5348,40 +5348,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>0.84</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR</t>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>388.22</v>
+        <v>389.06</v>
       </c>
     </row>
     <row r="15">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-388.22</v>
+        <v>-389.06</v>
       </c>
     </row>
     <row r="16">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Oktober" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_November" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Dezember" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Jahresgesamt" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +50,10 @@
     </font>
     <font>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -97,6 +102,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2768,6 +2775,338 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monat</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Umsatz netto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ausgabe netto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gewinn/Verlust</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Zahlungen ohne Beleg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01_Januar</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-34.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02_Februar</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-44.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03_Maerz</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-81.90000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04_April</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-98.15000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05_Mai</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-172.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06_Juni</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>142.39</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-142.39</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07_Juli</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>156.69</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-156.69</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08_August</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>180.07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-80.06999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09_September</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>389.06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-389.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10_Oktober</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>425</v>
+      </c>
+      <c r="C11" t="n">
+        <v>237.17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>187.83</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11_November</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>425</v>
+      </c>
+      <c r="C12" t="n">
+        <v>728.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-303.88</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12_Dezember</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>207.23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3792.77</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>GESAMTUMSATZ netto (Jahr):</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>GESAMTAUSGABEN netto (Jahr):</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2474.29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>GESAMTNETTOGEWINN/-VERLUST (Jahr):</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2475.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (Jahr):</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>HINWEIS: Melia-Hotel-Rechnung (Benito Ferrise, 82,99 EUR, 11.09.) ist noch offen -</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>sobald gefunden, muss diese Gesamtrechnung neu berechnet werden.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -868,78 +868,78 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TRIATHLON TRANSFER GMBH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C6" s="2" t="n">
         <v>130.34</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Nein - Finanzamt (steuerneutral)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Receipt-2265-8647.pdf</t>
+          <t>Invoice-GMM5S7YE-0001.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,17 +1891,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Invoice-GMM5S7YE-0001.pdf</t>
+          <t>Receipt-2265-8647.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
+          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
+          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
+          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,17 +2287,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
+          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2649,83 +2649,83 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Haufe Service Center GmbH via Mollie</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Benito Ferrise</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Benito Ferrise</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH via Mollie</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
       </c>
     </row>
@@ -2961,10 +2961,10 @@
         <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>180.07</v>
+        <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-80.06999999999999</v>
+        <v>-498.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2980,13 +2980,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>389.06</v>
+        <v>502.3</v>
       </c>
       <c r="D10" t="n">
-        <v>-389.06</v>
+        <v>-502.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2474.29</v>
+        <v>3005.68</v>
       </c>
     </row>
     <row r="17">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2475.71</v>
+        <v>1944.32</v>
       </c>
     </row>
     <row r="18">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19"/>
@@ -4827,7 +4827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4923,134 +4923,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Domain webwokr.pdf</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wix.com LTD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | Domain webwokr.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Google Workspace 2025.pdf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wix.com LTD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | Google Workspace 2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>3.63</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>39</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Apify_Invoice_202508060773.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>APIFY* SUBSCRIPTION</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.84</v>
+        <v>78.38</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+          <t>Nein - Finanzamt (steuerneutral)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5061,19 +5065,19 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5082,7 +5086,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.9</v>
+        <v>39</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5096,64 +5100,60 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lexoffice 08 25.pdf</t>
+          <t>Apify_Invoice_202508060773.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haufe Service Center GmbH</t>
+          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
+          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Invoice-BCE54405-0015.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>UZR*digistore24.com</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5161,6 +5161,9 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>21.9</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -5173,174 +5176,254 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Premium Paket 2025.pdf</t>
+          <t>Lexoffice 08 25.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wix.com</t>
+          <t>Haufe Service Center GmbH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Wix.com</t>
+          <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0015.pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>240</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Premium Paket 2025.pdf</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wix.com</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Wix.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>100</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Rechnung Joel Wagner.pdf</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>47</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Funnelcockpit_2.pdf</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Umsatz netto:</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Ausgabe netto:</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>180.07</v>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-80.06999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Ausgabe netto:</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>598.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>GEWINN/VERLUST:</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-498.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C19" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5355,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -5364,7 +5447,7 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="53" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -5571,36 +5654,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rechnung_RE0009 (1).pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Hotel Melia Frankfurt am Main | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -5689,158 +5776,198 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LNKD_INVOICE_789144507558.pdf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LinkedIn Ireland Unlimited Company</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | LNKD_INVOICE_789144507558.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>0.84</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>7.55</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>47</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Rechnung_TJC9SRX6_I-74230203-de.pdf</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Umsatz netto:</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>389.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-389.06</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>GEWINN/VERLUST:</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-502.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2</v>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -2904,10 +2904,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>172.9</v>
+        <v>167.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-172.9</v>
+        <v>-167.9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2942,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>156.69</v>
+        <v>151.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-156.69</v>
+        <v>-151.69</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3005.68</v>
+        <v>2995.68</v>
       </c>
     </row>
     <row r="17">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1944.32</v>
+        <v>1954.32</v>
       </c>
     </row>
     <row r="18">
@@ -3790,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3798,7 +3798,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4088,7 +4088,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>17.73</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4106,103 +4106,63 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
+          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>172.9</v>
+        <v>-167.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-172.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4484,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4492,7 +4452,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4735,84 +4695,44 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PNL Fintech B.V.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>156.69</v>
+        <v>-151.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-156.69</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,14 +49,11 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +72,6 @@
         <bgColor rgb="001F2937"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,15 +85,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1191,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1407,45 +1397,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>H_32869079.pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1454,7 +1448,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.16</v>
+        <v>25</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,33 +1462,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>H_32869079.pdf</t>
+          <t>Triathlon Miete.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,100 +1502,100 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Triathlon Miete.pdf</t>
+          <t>Rechnung RE250007.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>425</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250007.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>H_33541164.pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1610,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.99</v>
+        <v>97.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,99 +1618,59 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>H_33541164.pdf</t>
+          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>PNL Fintech B.V.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PNL Fintech B.V.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
           <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>425</v>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>425</v>
+        <v>720.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>728.88</v>
+        <v>-295.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-303.88</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2304,7 +2258,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2313,7 +2267,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.92</v>
+        <v>11</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,24 +2281,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(kein Originalbeleg - akzeptiert)</t>
+          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2353,7 +2307,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,24 +2321,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
+          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2393,7 +2347,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2407,100 +2361,100 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
+          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE*WORKSPACE</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>GOOGLE*WORKSPACE</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>GOOGLE*WORKSPACE</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TRIATHLON TRANSFER GMBH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2509,7 +2463,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>17.99</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,33 +2477,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Triathlon Miete.pdf</t>
+          <t>H_34974301.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+          <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17.99</v>
+        <v>4000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2563,210 +2517,170 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>H_34974301.pdf</t>
+          <t>Rechnung RE250009.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>Joel Wagner</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rechnung RE250009.pdf</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Joel Wagner</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Benito Ferrise</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Haufe Service Center GmbH via Mollie</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH via Mollie</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Benito Ferrise</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+    </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4000</v>
+        <v>189.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>207.23</v>
+        <v>3810.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3792.77</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2885,13 +2799,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>98.15000000000001</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-98.15000000000001</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3018,13 +2932,13 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>728.88</v>
+        <v>720.24</v>
       </c>
       <c r="D12" t="n">
-        <v>-303.88</v>
+        <v>-295.24</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3037,10 +2951,10 @@
         <v>4000</v>
       </c>
       <c r="C13" t="n">
-        <v>207.23</v>
+        <v>189.31</v>
       </c>
       <c r="D13" t="n">
-        <v>3792.77</v>
+        <v>3810.69</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -3048,55 +2962,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GESAMTUMSATZ netto (Jahr):</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>4950</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>GESAMTAUSGABEN netto (Jahr):</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>2995.68</v>
+      <c r="B16" s="4" t="n">
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>GESAMTNETTOGEWINN/-VERLUST (Jahr):</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>1954.32</v>
+      <c r="B17" s="4" t="n">
+        <v>1991.68</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>davon Zahlungen ohne Beleg (Jahr):</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>16</v>
+      <c r="B18" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>HINWEIS: Melia-Hotel-Rechnung (Benito Ferrise, 82,99 EUR, 11.09.) ist noch offen -</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>sobald gefunden, muss diese Gesamtrechnung neu berechnet werden.</t>
         </is>
@@ -3527,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3583,45 +3497,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>ZOHO-ZOHO CORP</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>ZOHO-ZOHO CORP</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Instantly 04 25.pdf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3630,7 +3548,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.13</v>
+        <v>33.32</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3644,7 +3562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Instantly 04 25.pdf</t>
+          <t>Instantly 041 25.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3661,7 +3579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3670,7 +3588,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33.32</v>
+        <v>19.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3679,104 +3597,64 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Instantly 041 25.pdf</t>
+          <t>Lexoffice 04 25.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Haufe Service Center GmbH</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lexoffice 04 25.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>6081.7571.6196 Haufe Service Center | GmbH lx2025040088805 KHYY-YNLG | Lexware Office L | 67f32b8cb70fd8129780e042 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98.15000000000001</v>
+        <v>-87.34999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-98.15000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -93,7 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2695,10 +2694,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -2999,21 +2998,6 @@
       </c>
       <c r="B18" s="4" t="n">
         <v>14</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>HINWEIS: Melia-Hotel-Rechnung (Benito Ferrise, 82,99 EUR, 11.09.) ist noch offen -</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>sobald gefunden, muss diese Gesamtrechnung neu berechnet werden.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>598.22</v>
+        <v>698.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-498.22</v>
+        <v>-698.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="16">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2958.32</v>
+        <v>3058.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1991.68</v>
+        <v>1791.68</v>
       </c>
     </row>
     <row r="18">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Umsatz</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>598.22</v>
+        <v>698.22</v>
       </c>
     </row>
     <row r="18">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-498.22</v>
+        <v>-698.22</v>
       </c>
     </row>
     <row r="19">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>698.22</v>
+        <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-698.22</v>
+        <v>-498.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="16">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3058.32</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1791.68</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="18">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>698.22</v>
+        <v>598.22</v>
       </c>
     </row>
     <row r="18">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-698.22</v>
+        <v>-498.22</v>
       </c>
     </row>
     <row r="19">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>97.2</v>
+        <v>115.67</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>720.24</v>
+        <v>738.71</v>
       </c>
     </row>
     <row r="15">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-295.24</v>
+        <v>-313.71</v>
       </c>
     </row>
     <row r="16">
@@ -2931,10 +2931,10 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>720.24</v>
+        <v>738.71</v>
       </c>
       <c r="D12" t="n">
-        <v>-295.24</v>
+        <v>-313.71</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2958.32</v>
+        <v>2976.79</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1991.68</v>
+        <v>1973.21</v>
       </c>
     </row>
     <row r="18">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -688,7 +688,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -897,36 +897,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>130.34</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
     </row>
     <row r="14">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
     </row>
     <row r="16">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2852,16 +2852,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="C8" t="n">
         <v>151.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2871,16 +2871,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
       <c r="C9" t="n">
         <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2909,16 +2909,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
       <c r="C11" t="n">
         <v>237.17</v>
       </c>
       <c r="D11" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
     </row>
     <row r="16">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="18">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4312,8 +4312,8 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -4522,36 +4522,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="9">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
     </row>
     <row r="11">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4616,7 +4616,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -4821,36 +4821,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
     </row>
     <row r="17">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
     </row>
     <row r="19">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025_monatlich_netto.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115.67</v>
+        <v>97.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
     </row>
     <row r="15">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
     </row>
     <row r="16">
@@ -2931,10 +2931,10 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
       <c r="D12" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="18">
